--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8446-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8446-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA7400E1-F426-40E4-94D4-24E3034F1122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A7CD2AA-C1B8-49C8-9998-DA6F01ED3994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{CE6FF06E-2D6E-45A5-8D66-9FDE47233B9B}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{074A4CC8-DD02-4D81-99A6-4F4C823E4B80}"/>
   </bookViews>
   <sheets>
     <sheet name="8446-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1505,24 +1505,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88237AB4-623F-4D11-A697-96A685D61AE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DAF7026-75F6-4439-B2D4-D38C6A5908EA}">
   <dimension ref="A1:X34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="8.125" customWidth="1"/>
-    <col min="22" max="23" width="6.75" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
+    <col min="22" max="23" width="5.88671875" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1556,7 +1556,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1592,7 +1592,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1712,7 +1712,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2021</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2020</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>8.31</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2019</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2018</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2017</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2016</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2015</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2014</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2013</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2012</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35" t="s">
         <v>56</v>
       </c>
